--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="O2" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P2" t="n">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P3" t="n">
-        <v>4.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="O2" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P2" t="n">
-        <v>4.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="O3" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P3" t="n">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="O2" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P2" t="n">
-        <v>4.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="O3" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P3" t="n">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU5"/>
+  <dimension ref="A1:AU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,27 +678,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46181.83333333334</v>
+        <v>46181.54166666666</v>
       </c>
     </row>
     <row r="3">
@@ -837,27 +837,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>46181.83333333334</v>
+        <v>46181.625</v>
       </c>
     </row>
     <row r="4">
@@ -996,27 +996,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>46181.85416666666</v>
+        <v>46181.625</v>
       </c>
     </row>
     <row r="5">
@@ -1155,156 +1155,792 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Morocco Botola Pro</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Olympique Dcheïra</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hassania Agadir</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="3" t="n">
+        <v>46181.70833333334</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="3" t="n">
+        <v>46181.83333333334</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="3" t="n">
+        <v>46181.83333333334</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>20:30</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Chile Primera B</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Unión Española</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Unión San Felipe</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="3" t="n">
+        <v>46181.85416666666</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Deportes Temuco</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Curicó Unido</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" s="3" t="n">
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="3" t="n">
         <v>46181.85416666666</v>
       </c>
     </row>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P6" t="n">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P7" t="n">
-        <v>4.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="O6" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="P6" t="n">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="O7" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="P7" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="O6" t="n">
-        <v>2.81</v>
+        <v>3.02</v>
       </c>
       <c r="P6" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="S6" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
         <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE6" t="n">
         <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="O7" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="U7" t="n">
         <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE7" t="n">
         <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.71</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="O6" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="P6" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="S6" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="U6" t="n">
         <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
         <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.71</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="O7" t="n">
-        <v>2.81</v>
+        <v>3.02</v>
       </c>
       <c r="P7" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="S7" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="T7" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
         <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE7" t="n">
         <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="O6" t="n">
-        <v>2.81</v>
+        <v>3.02</v>
       </c>
       <c r="P6" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="S6" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
         <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE6" t="n">
         <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="O7" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="U7" t="n">
         <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE7" t="n">
         <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.71</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="O6" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="P6" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="S6" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="U6" t="n">
         <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
         <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.71</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="O7" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="S7" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="T7" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
         <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE7" t="n">
         <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="O6" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="S6" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
         <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE6" t="n">
         <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="U7" t="n">
         <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE7" t="n">
         <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.71</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="O8" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>3.31</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="P9" t="n">
-        <v>3.31</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="P6" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="S6" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="U6" t="n">
         <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
         <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.71</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="O7" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="S7" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="T7" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
         <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE7" t="n">
         <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="Q6" t="n">
         <v>2.74</v>
@@ -1562,7 +1562,7 @@
         <v>2.47</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
         <v>4.6</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="P8" t="n">
-        <v>3.31</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="O9" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>3.31</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="S6" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
         <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AB6" t="n">
         <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE6" t="n">
         <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="U7" t="n">
         <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
         <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE7" t="n">
         <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.71</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="O8" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>3.31</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="P9" t="n">
-        <v>3.31</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="S6" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="U6" t="n">
         <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
         <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
         <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.71</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="S7" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="T7" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
         <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AB7" t="n">
         <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE7" t="n">
         <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="S6" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
         <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AB6" t="n">
         <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE6" t="n">
         <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="U7" t="n">
         <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
         <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE7" t="n">
         <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.71</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="P8" t="n">
-        <v>3.31</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="O9" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>3.31</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="O8" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>3.31</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="P9" t="n">
-        <v>3.31</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="O3" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P3" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P4" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="S6" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="U6" t="n">
         <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
         <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
         <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.71</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="S7" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="T7" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
         <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AB7" t="n">
         <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE7" t="n">
         <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
         <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="O9" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="O2" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="O3" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="P3" t="n">
-        <v>5.5</v>
+        <v>5.57</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="O4" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="P4" t="n">
-        <v>6.8</v>
+        <v>5.13</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="P5" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="S6" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
         <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AB6" t="n">
         <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE6" t="n">
         <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="U7" t="n">
         <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
         <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE7" t="n">
         <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.71</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -1526,7 +1526,7 @@
         <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q7" t="n">
         <v>2.74</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="O9" t="n">
         <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="O3" t="n">
-        <v>3.64</v>
+        <v>3.44</v>
       </c>
       <c r="P3" t="n">
-        <v>5.57</v>
+        <v>5.13</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="O4" t="n">
-        <v>3.44</v>
+        <v>3.64</v>
       </c>
       <c r="P4" t="n">
-        <v>5.13</v>
+        <v>5.57</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.7</v>
+        <v>2.07</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.07</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -1364,10 +1364,10 @@
         <v>2.37</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="P6" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="P7" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="Q7" t="n">
         <v>2.74</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="O3" t="n">
-        <v>3.44</v>
+        <v>3.64</v>
       </c>
       <c r="P3" t="n">
-        <v>5.13</v>
+        <v>5.57</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="O4" t="n">
-        <v>3.64</v>
+        <v>3.44</v>
       </c>
       <c r="P4" t="n">
-        <v>5.57</v>
+        <v>5.13</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="O2" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>4.33</v>
+        <v>3.87</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.64</v>
+        <v>3.94</v>
       </c>
       <c r="P3" t="n">
-        <v>5.57</v>
+        <v>6.33</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1043,49 +1043,49 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.61</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="P4" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.65</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="O3" t="n">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>6.33</v>
+        <v>4.6</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3.94</v>
       </c>
       <c r="P4" t="n">
-        <v>4.6</v>
+        <v>6.33</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="O6" t="n">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="P6" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="S6" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="U6" t="n">
         <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
         <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
         <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.71</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>3.15</v>
+        <v>2.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="S7" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="T7" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
         <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AB7" t="n">
         <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE7" t="n">
         <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,49 +1838,49 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.75</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -721,17 +721,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
-        <v>3.87</v>
+        <v>5.25</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46181.54166666666</v>
@@ -852,16 +852,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -873,24 +873,24 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.76</v>
       </c>
       <c r="P3" t="n">
-        <v>4.6</v>
+        <v>5.42</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -945,14 +945,14 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46181.625</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="O4" t="n">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>6.33</v>
+        <v>5.25</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC6" t="n">
         <v>4.4</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P7" t="n">
         <v>2.87</v>
@@ -1562,7 +1562,7 @@
         <v>2.47</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC7" t="n">
         <v>4.6</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -867,13 +867,13 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="O3" t="n">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>5.42</v>
+        <v>5.25</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -945,7 +945,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['45+7']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -966,25 +966,25 @@
         <v>5</v>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.19</v>
+        <v>1.97</v>
       </c>
       <c r="AS3" t="n">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="AT3" t="n">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46181.625</v>
@@ -1011,16 +1011,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -1032,24 +1032,24 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3.76</v>
       </c>
       <c r="P4" t="n">
-        <v>5.25</v>
+        <v>5.42</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1104,14 +1104,14 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
@@ -1122,28 +1122,28 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46181.625</v>
@@ -1182,13 +1182,13 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
@@ -1281,28 +1281,28 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46181.70833333334</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="O6" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>3.15</v>
+        <v>2.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="S6" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
         <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AB6" t="n">
         <v>1.47</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE6" t="n">
         <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="O7" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="P7" t="n">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="U7" t="n">
         <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
         <v>1.47</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE7" t="n">
         <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.71</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.65</v>
+        <v>2.09</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.09</v>
+        <v>1.69</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P9" t="n">
-        <v>3.25</v>
+        <v>4.67</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB9" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.75</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-06-08.xlsx
+++ b/jogos_2026-06-08.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -867,14 +867,14 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.76</v>
       </c>
       <c r="P3" t="n">
-        <v>5.25</v>
+        <v>5.42</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -945,7 +945,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>['45+7']</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -966,25 +966,25 @@
         <v>5</v>
       </c>
       <c r="AN3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AP3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.68</v>
+        <v>1.42</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.97</v>
+        <v>1.19</v>
       </c>
       <c r="AS3" t="n">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="AT3" t="n">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46181.625</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1026,13 +1026,13 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="O4" t="n">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>5.42</v>
+        <v>5.25</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['45+7']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1125,25 +1125,25 @@
         <v>5</v>
       </c>
       <c r="AN4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.19</v>
+        <v>1.97</v>
       </c>
       <c r="AS4" t="n">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="AT4" t="n">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46181.625</v>
@@ -1329,22 +1329,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1357,111 +1357,111 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="P6" t="n">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="S6" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="U6" t="n">
         <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
         <v>1.47</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
         <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.71</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46181.83333333334</v>
@@ -1488,139 +1488,139 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="O7" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="P7" t="n">
-        <v>3.15</v>
+        <v>2.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="S7" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="T7" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
         <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AB7" t="n">
         <v>1.47</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE7" t="n">
         <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33', '73']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46181.83333333334</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.09</v>
+        <v>1.69</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>3.25</v>
+        <v>4.67</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB8" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.69</v>
+        <v>2.09</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>4.67</v>
+        <v>3.25</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
